--- a/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 1,62</t>
+          <t>-22,87; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,07; -2,92</t>
+          <t>-26,72; -2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 0,0</t>
+          <t>-15,8; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 0,0</t>
+          <t>-16,44; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 0,54</t>
+          <t>-13,21; 0,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -1,43</t>
+          <t>-13,65; -1,39</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 0,0</t>
+          <t>-19,49; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 5,55</t>
+          <t>-16,44; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,94</t>
+          <t>0,0; 18,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 0,0</t>
+          <t>-10,05; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 7,79</t>
+          <t>-5,46; 7,79</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 1,9</t>
+          <t>-38,62; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-38,18; -4,66</t>
+          <t>-42,64; -4,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 0,0</t>
+          <t>-16,65; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 0,0</t>
+          <t>-16,55; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 1,68</t>
+          <t>-15,35; 0,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -1,74</t>
+          <t>-17,79; -1,98</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 5,21</t>
+          <t>-6,61; 5,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 3,03</t>
+          <t>-8,36; 3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 1,67</t>
+          <t>-7,81; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 3,32</t>
+          <t>-5,67; 3,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,51</t>
+          <t>-5,03; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,65</t>
+          <t>-4,8; 2,35</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 0,0</t>
+          <t>-20,2; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 0,0</t>
+          <t>-20,2; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 15,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,12</t>
+          <t>-5,01; 3,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-9,95; 0,0</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 17,34</t>
+          <t>-12,8; 17,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 0,0</t>
+          <t>-28,88; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 9,66</t>
+          <t>-8,1; 9,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 0,0</t>
+          <t>-13,99; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -0,96</t>
+          <t>-8,54; -0,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -1,81</t>
+          <t>-9,06; -2,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,05</t>
+          <t>-2,91; 2,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,51</t>
+          <t>-3,06; 1,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,1</t>
+          <t>-4,22; 0,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,61</t>
+          <t>-4,96; -0,64</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -2,87</t>
+          <t>-90,75; -14,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-95,16; -32,89</t>
+          <t>-100,0; -35,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-85,9; 273,72</t>
+          <t>-82,15; 345,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 347,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 14,23</t>
+          <t>-79,51; 14,8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-89,72; -5,53</t>
+          <t>-89,59; -6,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 1,77</t>
+          <t>-23,1; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,72; -2,93</t>
+          <t>-28,16; -2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 0,0</t>
+          <t>-12,92; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 0,0</t>
+          <t>-14,36; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 0,09</t>
+          <t>-12,56; 0,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -1,39</t>
+          <t>-14,77; -1,42</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 0,0</t>
+          <t>-22,42; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 5,33</t>
+          <t>-16,26; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,34</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,0</t>
+          <t>-11,89; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 7,79</t>
+          <t>-5,38; 8,13</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 2,81</t>
+          <t>-33,75; 2,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -4,53</t>
+          <t>-37,02; -4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 0,0</t>
+          <t>-15,29; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 0,0</t>
+          <t>-13,07; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 0,5</t>
+          <t>-15,01; 0,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -1,98</t>
+          <t>-17,67; -1,9</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,41</t>
+          <t>-6,68; 5,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 3,13</t>
+          <t>-8,63; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 1,8</t>
+          <t>-8,5; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,32</t>
+          <t>-5,97; 3,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,38</t>
+          <t>-4,71; 2,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,35</t>
+          <t>-4,61; 2,57</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 0,0</t>
+          <t>-17,93; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 0,0</t>
+          <t>-17,93; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,65</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,74</t>
+          <t>-4,96; 4,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 0,0</t>
+          <t>-7,75; 0,0</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 17,71</t>
+          <t>-12,84; 17,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 0,0</t>
+          <t>-27,82; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 9,66</t>
+          <t>-9,77; 9,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 0,0</t>
+          <t>-14,79; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,95</t>
+          <t>-8,63; -0,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -2,14</t>
+          <t>-9,42; -1,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,26</t>
+          <t>-2,68; 2,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,98</t>
+          <t>-3,53; 1,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,22</t>
+          <t>-4,31; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -0,64</t>
+          <t>-4,95; -0,56</t>
         </is>
       </c>
     </row>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-90,75; -14,97</t>
+          <t>-92,22; -5,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -35,99</t>
+          <t>-100,0; -33,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-82,15; 345,46</t>
+          <t>-85,8; 520,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,51; 14,8</t>
+          <t>-79,25; 11,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-89,59; -6,3</t>
+          <t>-87,65; -7,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Clase-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-7,4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-9,81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 2,01</t>
+          <t>-13,09; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,16; -2,95</t>
+          <t>-14,94; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 0,0</t>
+          <t>-23,95; 1,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 0,0</t>
+          <t>-27,07; -2,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 0,63</t>
+          <t>-12,61; 0,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -1,42</t>
+          <t>-13,75; -1,43</t>
         </is>
       </c>
     </row>
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-75,46%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-6,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-3,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 5,67</t>
+          <t>0,0; 17,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,35; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>-15,91; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 0,0</t>
+          <t>-11,47; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 8,13</t>
+          <t>-6,35; 7,79</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-51,99%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,04</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-11,96</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-15,89</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 2,29</t>
+          <t>-17,29; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-37,02; -4,47</t>
+          <t>-13,25; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 0,0</t>
+          <t>-34,03; 1,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 0,0</t>
+          <t>-38,18; -4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 0,24</t>
+          <t>-14,62; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -1,9</t>
+          <t>-16,66; -1,74</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-75,27%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-1,33</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 5,0</t>
+          <t>-8,48; 1,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,8</t>
+          <t>-7,38; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 1,79</t>
+          <t>-6,79; 5,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,28</t>
+          <t>-8,16; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,35</t>
+          <t>-5,02; 2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,57</t>
+          <t>-5,17; 2,65</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-51,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-0,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-39,57%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-51,62%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-12,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-5,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-5,54</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,58</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 0,0</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>-17,31; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,31; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 4,25</t>
+          <t>-4,83; 4,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,0</t>
+          <t>-7,5; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,66</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-5,66</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,09; 17,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,03; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 17,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 9,75</t>
+          <t>-10,21; 9,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 0,0</t>
+          <t>-19,36; 0,0</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-4,34</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-5,07</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -0,85</t>
+          <t>-3,1; 2,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,42; -1,93</t>
+          <t>-3,6; 1,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,45</t>
+          <t>-8,61; -0,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,97</t>
+          <t>-9,41; -1,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,14</t>
+          <t>-4,38; 0,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -0,56</t>
+          <t>-4,98; -0,61</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-3,89%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-26,92%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-70,14%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-81,81%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-3,89%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-26,92%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-92,22; -5,45</t>
+          <t>-85,9; 273,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,06</t>
+          <t>-100,0; 347,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 520,58</t>
+          <t>-92,76; -2,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-95,16; -32,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 11,06</t>
+          <t>-79,39; 14,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,65; -7,98</t>
+          <t>-89,72; -5,53</t>
         </is>
       </c>
     </row>
